--- a/Data/CERP_PBC_WQ_Summary_Data.xlsx
+++ b/Data/CERP_PBC_WQ_Summary_Data.xlsx
@@ -1468,7 +1468,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1480,31 +1480,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1527,7 +1518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1563,7 +1554,6 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4795,7 +4785,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B29" t="n">
@@ -4804,7 +4794,7 @@
       <c r="C29" t="n">
         <v>5.52</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="E29" t="n">
@@ -4813,7 +4803,7 @@
       <c r="F29" t="n">
         <v>6.1</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="H29" t="n">
@@ -4825,7 +4815,7 @@
       <c r="J29" t="n">
         <v>5.72</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="L29" t="n">
@@ -4837,7 +4827,7 @@
       <c r="N29" t="n">
         <v>6.89</v>
       </c>
-      <c r="O29" s="13" t="n">
+      <c r="O29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="P29" t="n">
@@ -4849,7 +4839,7 @@
       <c r="R29" t="n">
         <v>6.22</v>
       </c>
-      <c r="S29" s="13" t="n">
+      <c r="S29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="T29" t="n">
@@ -4861,7 +4851,7 @@
       <c r="V29" t="n">
         <v>8.46</v>
       </c>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="X29" t="n">
@@ -4873,7 +4863,7 @@
       <c r="Z29" t="n">
         <v>5.88</v>
       </c>
-      <c r="AA29" s="13" t="n">
+      <c r="AA29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AB29" t="n">
@@ -4885,7 +4875,7 @@
       <c r="AD29" t="n">
         <v>6.06</v>
       </c>
-      <c r="AE29" s="13" t="n">
+      <c r="AE29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AF29" t="n">
@@ -4899,7 +4889,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -4908,7 +4898,7 @@
       <c r="C30" t="n">
         <v>5.72</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="E30" t="n">
@@ -4917,7 +4907,7 @@
       <c r="F30" t="n">
         <v>5.05</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="H30" t="n">
@@ -4929,7 +4919,7 @@
       <c r="J30" t="n">
         <v>7.13</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -4941,7 +4931,7 @@
       <c r="N30" t="n">
         <v>5.81</v>
       </c>
-      <c r="O30" s="13" t="n">
+      <c r="O30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="P30" t="n">
@@ -4953,7 +4943,7 @@
       <c r="R30" t="n">
         <v>6.09</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="T30" t="n">
@@ -4965,7 +4955,7 @@
       <c r="V30" t="n">
         <v>7.12</v>
       </c>
-      <c r="W30" s="13" t="n">
+      <c r="W30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="X30" t="n">
@@ -4977,7 +4967,7 @@
       <c r="Z30" t="n">
         <v>4.98</v>
       </c>
-      <c r="AA30" s="13" t="n">
+      <c r="AA30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AB30" t="n">
@@ -4989,7 +4979,7 @@
       <c r="AD30" t="n">
         <v>4.85</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -5003,7 +4993,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -5012,7 +5002,7 @@
       <c r="C31" t="n">
         <v>5.01</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="E31" t="n">
@@ -5021,7 +5011,7 @@
       <c r="F31" t="n">
         <v>4.22</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="H31" t="n">
@@ -5033,7 +5023,7 @@
       <c r="J31" t="n">
         <v>6.61</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -5045,7 +5035,7 @@
       <c r="N31" t="n">
         <v>6.02</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="P31" t="n">
@@ -5057,7 +5047,7 @@
       <c r="R31" t="n">
         <v>5.17</v>
       </c>
-      <c r="S31" s="13" t="n">
+      <c r="S31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="T31" t="n">
@@ -5069,7 +5059,7 @@
       <c r="V31" t="n">
         <v>4.31</v>
       </c>
-      <c r="W31" s="13" t="n">
+      <c r="W31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="X31" t="n">
@@ -5081,7 +5071,7 @@
       <c r="Z31" t="n">
         <v>5.59</v>
       </c>
-      <c r="AA31" s="13" t="n">
+      <c r="AA31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AB31" t="n">
@@ -5093,7 +5083,7 @@
       <c r="AD31" t="n">
         <v>6.71</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -9102,7 +9092,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -9117,7 +9107,7 @@
       <c r="E30" t="n">
         <v>100</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="G30" t="n">
@@ -9132,7 +9122,7 @@
       <c r="J30" t="n">
         <v>100</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -9147,7 +9137,7 @@
       <c r="O30" t="n">
         <v>100</v>
       </c>
-      <c r="P30" s="13" t="n">
+      <c r="P30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="Q30" t="n">
@@ -9162,7 +9152,7 @@
       <c r="T30" t="n">
         <v>100</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="V30" t="n">
@@ -9177,7 +9167,7 @@
       <c r="Y30" t="n">
         <v>100</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="AA30" t="n">
@@ -9192,7 +9182,7 @@
       <c r="AD30" t="n">
         <v>100</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -9207,7 +9197,7 @@
       <c r="AI30" t="n">
         <v>100</v>
       </c>
-      <c r="AJ30" s="13" t="n">
+      <c r="AJ30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AK30" t="n">
@@ -9222,7 +9212,7 @@
       <c r="AN30" t="n">
         <v>100</v>
       </c>
-      <c r="AO30" s="13" t="n">
+      <c r="AO30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AP30" t="n">
@@ -9239,7 +9229,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -9254,7 +9244,7 @@
       <c r="E31" t="n">
         <v>100</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="G31" t="n">
@@ -9269,7 +9259,7 @@
       <c r="J31" t="n">
         <v>100</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -9284,7 +9274,7 @@
       <c r="O31" t="n">
         <v>100</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="Q31" t="n">
@@ -9299,7 +9289,7 @@
       <c r="T31" t="n">
         <v>100</v>
       </c>
-      <c r="U31" s="13" t="n">
+      <c r="U31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="V31" t="n">
@@ -9314,7 +9304,7 @@
       <c r="Y31" t="n">
         <v>81.82</v>
       </c>
-      <c r="Z31" s="13" t="n">
+      <c r="Z31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="AA31" t="n">
@@ -9329,7 +9319,7 @@
       <c r="AD31" t="n">
         <v>100</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -9344,7 +9334,7 @@
       <c r="AI31" t="n">
         <v>100</v>
       </c>
-      <c r="AJ31" s="13" t="n">
+      <c r="AJ31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AK31" t="n">
@@ -9359,7 +9349,7 @@
       <c r="AN31" t="n">
         <v>100</v>
       </c>
-      <c r="AO31" s="13" t="n">
+      <c r="AO31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AP31" t="n">
@@ -20858,7 +20848,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -20873,7 +20863,7 @@
       <c r="E30" t="n">
         <v>5.72</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="G30" t="n">
@@ -20888,7 +20878,7 @@
       <c r="J30" t="n">
         <v>5.05</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -20903,7 +20893,7 @@
       <c r="O30" t="n">
         <v>7.13</v>
       </c>
-      <c r="P30" s="13" t="n">
+      <c r="P30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="Q30" t="n">
@@ -20918,7 +20908,7 @@
       <c r="T30" t="n">
         <v>6.88</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="V30" t="n">
@@ -20933,7 +20923,7 @@
       <c r="Y30" t="n">
         <v>6.66</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="AA30" t="n">
@@ -20948,7 +20938,7 @@
       <c r="AD30" t="n">
         <v>7.29</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -20963,7 +20953,7 @@
       <c r="AI30" t="n">
         <v>5.18</v>
       </c>
-      <c r="AJ30" s="13" t="n">
+      <c r="AJ30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AK30" t="n">
@@ -20978,7 +20968,7 @@
       <c r="AN30" t="n">
         <v>5.4</v>
       </c>
-      <c r="AO30" s="13" t="n">
+      <c r="AO30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AP30" t="n">
@@ -20995,7 +20985,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -21010,7 +21000,7 @@
       <c r="E31" t="n">
         <v>7.04</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="G31" t="n">
@@ -21025,7 +21015,7 @@
       <c r="J31" t="n">
         <v>5.94</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -21040,7 +21030,7 @@
       <c r="O31" t="n">
         <v>6.61</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="Q31" t="n">
@@ -21055,7 +21045,7 @@
       <c r="T31" t="n">
         <v>6.02</v>
       </c>
-      <c r="U31" s="13" t="n">
+      <c r="U31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="V31" t="n">
@@ -21070,7 +21060,7 @@
       <c r="Y31" t="n">
         <v>7</v>
       </c>
-      <c r="Z31" s="13" t="n">
+      <c r="Z31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="AA31" t="n">
@@ -21085,7 +21075,7 @@
       <c r="AD31" t="n">
         <v>4.65</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -21100,7 +21090,7 @@
       <c r="AI31" t="n">
         <v>6.16</v>
       </c>
-      <c r="AJ31" s="13" t="n">
+      <c r="AJ31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AK31" t="n">
@@ -21115,7 +21105,7 @@
       <c r="AN31" t="n">
         <v>6.71</v>
       </c>
-      <c r="AO31" s="13" t="n">
+      <c r="AO31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AP31" t="n">
@@ -31466,7 +31456,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="B27" t="n">
@@ -31475,13 +31465,13 @@
       <c r="C27" t="n">
         <v>8.2799999999999994</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="E27" t="n">
         <v>9.0500000000000007</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="H27" t="n">
@@ -31493,7 +31483,7 @@
       <c r="J27" t="n">
         <v>8.17</v>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="K27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="L27" t="n">
@@ -31505,7 +31495,7 @@
       <c r="N27" t="n">
         <v>8.31</v>
       </c>
-      <c r="O27" s="13" t="n">
+      <c r="O27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="P27" t="n">
@@ -31517,7 +31507,7 @@
       <c r="R27" t="n">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S27" s="13" t="n">
+      <c r="S27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="T27" t="n">
@@ -31529,7 +31519,7 @@
       <c r="V27" t="n">
         <v>8.25</v>
       </c>
-      <c r="W27" s="13" t="n">
+      <c r="W27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="X27" t="n">
@@ -31541,7 +31531,7 @@
       <c r="Z27" t="n">
         <v>7.88</v>
       </c>
-      <c r="AA27" s="13" t="n">
+      <c r="AA27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="AB27" t="n">
@@ -31553,7 +31543,7 @@
       <c r="AD27" t="n">
         <v>7.85</v>
       </c>
-      <c r="AE27" s="13" t="n">
+      <c r="AE27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="AF27" t="n">
@@ -31567,13 +31557,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n">
+      <c r="A28" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="H28" t="n">
@@ -31585,7 +31575,7 @@
       <c r="J28" t="n">
         <v>8.39</v>
       </c>
-      <c r="K28" s="13" t="n">
+      <c r="K28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="L28" t="n">
@@ -31597,7 +31587,7 @@
       <c r="N28" t="n">
         <v>8.89</v>
       </c>
-      <c r="O28" s="13" t="n">
+      <c r="O28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="P28" t="n">
@@ -31609,7 +31599,7 @@
       <c r="R28" t="n">
         <v>8.0399999999999991</v>
       </c>
-      <c r="S28" s="13" t="n">
+      <c r="S28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="T28" t="n">
@@ -31621,7 +31611,7 @@
       <c r="V28" t="n">
         <v>8.18</v>
       </c>
-      <c r="W28" s="13" t="n">
+      <c r="W28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="X28" t="n">
@@ -31633,7 +31623,7 @@
       <c r="Z28" t="n">
         <v>7.89</v>
       </c>
-      <c r="AA28" s="13" t="n">
+      <c r="AA28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="AB28" t="n">
@@ -31645,7 +31635,7 @@
       <c r="AD28" t="n">
         <v>8.18</v>
       </c>
-      <c r="AE28" s="13" t="n">
+      <c r="AE28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="AF28" t="n">
@@ -31659,53 +31649,53 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="L29"/>
       <c r="M29"/>
       <c r="N29"/>
-      <c r="O29" s="13" t="n">
+      <c r="O29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29"/>
-      <c r="S29" s="13" t="n">
+      <c r="S29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29"/>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="X29"/>
       <c r="Y29"/>
       <c r="Z29"/>
-      <c r="AA29" s="13" t="n">
+      <c r="AA29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29"/>
-      <c r="AE29" s="13" t="n">
+      <c r="AE29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AF29"/>
@@ -31713,53 +31703,53 @@
       <c r="AH29"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30"/>
       <c r="C30"/>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30"/>
       <c r="M30"/>
       <c r="N30"/>
-      <c r="O30" s="13" t="n">
+      <c r="O30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30"/>
-      <c r="W30" s="13" t="n">
+      <c r="W30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="X30"/>
       <c r="Y30"/>
       <c r="Z30"/>
-      <c r="AA30" s="13" t="n">
+      <c r="AA30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30"/>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30"/>
@@ -31767,7 +31757,7 @@
       <c r="AH30"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -31776,7 +31766,7 @@
       <c r="C31" t="n">
         <v>7.89</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="E31" t="n">
@@ -31785,7 +31775,7 @@
       <c r="F31" t="n">
         <v>7.94</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="H31" t="n">
@@ -31797,7 +31787,7 @@
       <c r="J31" t="n">
         <v>8.1</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -31809,7 +31799,7 @@
       <c r="N31" t="n">
         <v>7.9</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="P31" t="n">
@@ -31821,7 +31811,7 @@
       <c r="R31" t="n">
         <v>7.9</v>
       </c>
-      <c r="S31" s="13" t="n">
+      <c r="S31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="T31" t="n">
@@ -31833,7 +31823,7 @@
       <c r="V31" t="n">
         <v>7.9</v>
       </c>
-      <c r="W31" s="13" t="n">
+      <c r="W31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="X31" t="n">
@@ -31845,7 +31835,7 @@
       <c r="Z31" t="n">
         <v>7.92</v>
       </c>
-      <c r="AA31" s="13" t="n">
+      <c r="AA31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AB31" t="n">
@@ -31857,7 +31847,7 @@
       <c r="AD31" t="n">
         <v>7.84</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -35455,7 +35445,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="B27" t="n">
@@ -35470,7 +35460,7 @@
       <c r="E27" t="n">
         <v>8.2799999999999994</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="G27" t="n">
@@ -35482,7 +35472,7 @@
       <c r="J27" t="n">
         <v>9.0500000000000007</v>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="K27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="L27" t="n">
@@ -35497,7 +35487,7 @@
       <c r="O27" t="n">
         <v>8.32</v>
       </c>
-      <c r="P27" s="13" t="n">
+      <c r="P27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="Q27" t="n">
@@ -35512,7 +35502,7 @@
       <c r="T27" t="n">
         <v>8.31</v>
       </c>
-      <c r="U27" s="13" t="n">
+      <c r="U27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="V27" t="n">
@@ -35527,7 +35517,7 @@
       <c r="Y27" t="n">
         <v>8.31</v>
       </c>
-      <c r="Z27" s="13" t="n">
+      <c r="Z27" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="AA27" t="n">
@@ -35542,7 +35532,7 @@
       <c r="AD27" t="n">
         <v>8.2899999999999991</v>
       </c>
-      <c r="AE27" s="13" t="n">
+      <c r="AE27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="AF27" t="n">
@@ -35557,7 +35547,7 @@
       <c r="AI27" t="n">
         <v>7.88</v>
       </c>
-      <c r="AJ27" s="13" t="n">
+      <c r="AJ27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="AK27" t="n">
@@ -35572,7 +35562,7 @@
       <c r="AN27" t="n">
         <v>7.99</v>
       </c>
-      <c r="AO27" s="13" t="n">
+      <c r="AO27" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="AP27" t="n">
@@ -35589,13 +35579,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n">
+      <c r="A28" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="K28" s="13" t="n">
+      <c r="K28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="L28" t="n">
@@ -35610,7 +35600,7 @@
       <c r="O28" t="n">
         <v>8.56</v>
       </c>
-      <c r="P28" s="13" t="n">
+      <c r="P28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="Q28" t="n">
@@ -35625,7 +35615,7 @@
       <c r="T28" t="n">
         <v>8.89</v>
       </c>
-      <c r="U28" s="13" t="n">
+      <c r="U28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="V28" t="n">
@@ -35640,7 +35630,7 @@
       <c r="Y28" t="n">
         <v>8.09</v>
       </c>
-      <c r="Z28" s="13" t="n">
+      <c r="Z28" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="AA28" t="n">
@@ -35655,7 +35645,7 @@
       <c r="AD28" t="n">
         <v>8.31</v>
       </c>
-      <c r="AE28" s="13" t="n">
+      <c r="AE28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="AF28" t="n">
@@ -35670,7 +35660,7 @@
       <c r="AI28" t="n">
         <v>8.02</v>
       </c>
-      <c r="AJ28" s="13" t="n">
+      <c r="AJ28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="AK28" t="n">
@@ -35685,7 +35675,7 @@
       <c r="AN28" t="n">
         <v>8.18</v>
       </c>
-      <c r="AO28" s="13" t="n">
+      <c r="AO28" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="AP28" t="n">
@@ -35702,7 +35692,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B29" t="e">
@@ -35711,7 +35701,7 @@
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="G29" t="e">
@@ -35720,7 +35710,7 @@
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="L29" t="e">
@@ -35729,7 +35719,7 @@
       <c r="M29"/>
       <c r="N29"/>
       <c r="O29"/>
-      <c r="P29" s="13" t="n">
+      <c r="P29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="Q29" t="e">
@@ -35738,7 +35728,7 @@
       <c r="R29"/>
       <c r="S29"/>
       <c r="T29"/>
-      <c r="U29" s="13" t="n">
+      <c r="U29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="V29" t="e">
@@ -35747,7 +35737,7 @@
       <c r="W29"/>
       <c r="X29"/>
       <c r="Y29"/>
-      <c r="Z29" s="13" t="n">
+      <c r="Z29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="AA29" t="e">
@@ -35756,7 +35746,7 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29"/>
-      <c r="AE29" s="13" t="n">
+      <c r="AE29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AF29" t="e">
@@ -35765,7 +35755,7 @@
       <c r="AG29"/>
       <c r="AH29"/>
       <c r="AI29"/>
-      <c r="AJ29" s="13" t="n">
+      <c r="AJ29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AK29" t="e">
@@ -35774,7 +35764,7 @@
       <c r="AL29"/>
       <c r="AM29"/>
       <c r="AN29"/>
-      <c r="AO29" s="13" t="n">
+      <c r="AO29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AP29" t="e">
@@ -35785,7 +35775,7 @@
       <c r="AS29"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="e">
@@ -35794,7 +35784,7 @@
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="G30" t="e">
@@ -35803,7 +35793,7 @@
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="e">
@@ -35812,7 +35802,7 @@
       <c r="M30"/>
       <c r="N30"/>
       <c r="O30"/>
-      <c r="P30" s="13" t="n">
+      <c r="P30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="Q30" t="e">
@@ -35821,7 +35811,7 @@
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="V30" t="e">
@@ -35830,7 +35820,7 @@
       <c r="W30"/>
       <c r="X30"/>
       <c r="Y30"/>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="AA30" t="e">
@@ -35839,7 +35829,7 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30"/>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="e">
@@ -35848,7 +35838,7 @@
       <c r="AG30"/>
       <c r="AH30"/>
       <c r="AI30"/>
-      <c r="AJ30" s="13" t="n">
+      <c r="AJ30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AK30" t="e">
@@ -35857,7 +35847,7 @@
       <c r="AL30"/>
       <c r="AM30"/>
       <c r="AN30"/>
-      <c r="AO30" s="13" t="n">
+      <c r="AO30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AP30" t="e">
@@ -35868,7 +35858,7 @@
       <c r="AS30"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -35883,7 +35873,7 @@
       <c r="E31" t="n">
         <v>8.08</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="G31" t="n">
@@ -35898,7 +35888,7 @@
       <c r="J31" t="n">
         <v>8</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -35913,7 +35903,7 @@
       <c r="O31" t="n">
         <v>8.1</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="Q31" t="n">
@@ -35928,7 +35918,7 @@
       <c r="T31" t="n">
         <v>7.93</v>
       </c>
-      <c r="U31" s="13" t="n">
+      <c r="U31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="V31" t="n">
@@ -35943,7 +35933,7 @@
       <c r="Y31" t="n">
         <v>8.1</v>
       </c>
-      <c r="Z31" s="13" t="n">
+      <c r="Z31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="AA31" t="n">
@@ -35958,7 +35948,7 @@
       <c r="AD31" t="n">
         <v>7.94</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -35973,7 +35963,7 @@
       <c r="AI31" t="n">
         <v>8.03</v>
       </c>
-      <c r="AJ31" s="13" t="n">
+      <c r="AJ31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AK31" t="n">
@@ -35988,7 +35978,7 @@
       <c r="AN31" t="n">
         <v>7.86</v>
       </c>
-      <c r="AO31" s="13" t="n">
+      <c r="AO31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AP31" t="n">
@@ -38939,7 +38929,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="B29" t="n">
@@ -38948,7 +38938,7 @@
       <c r="C29" t="n">
         <v>18.28</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="E29" t="n">
@@ -38957,7 +38947,7 @@
       <c r="F29" t="n">
         <v>33.45</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="H29" t="n">
@@ -38969,7 +38959,7 @@
       <c r="J29" t="n">
         <v>34.18</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="L29" t="n">
@@ -38981,7 +38971,7 @@
       <c r="N29" t="n">
         <v>33.07</v>
       </c>
-      <c r="O29" s="13" t="n">
+      <c r="O29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="P29" t="n">
@@ -38993,7 +38983,7 @@
       <c r="R29" t="n">
         <v>11.54</v>
       </c>
-      <c r="S29" s="13" t="n">
+      <c r="S29" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="T29" t="n">
@@ -39005,7 +38995,7 @@
       <c r="V29" t="n">
         <v>32.52</v>
       </c>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="X29" t="n">
@@ -39017,7 +39007,7 @@
       <c r="Z29" t="n">
         <v>9.67</v>
       </c>
-      <c r="AA29" s="13" t="n">
+      <c r="AA29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AB29" t="n">
@@ -39029,7 +39019,7 @@
       <c r="AD29" t="n">
         <v>3.91</v>
       </c>
-      <c r="AE29" s="13" t="n">
+      <c r="AE29" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="AF29" t="n">
@@ -39043,7 +39033,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -39052,7 +39042,7 @@
       <c r="C30" t="n">
         <v>14.34</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="E30" t="n">
@@ -39061,7 +39051,7 @@
       <c r="F30" t="n">
         <v>28.45</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="H30" t="n">
@@ -39073,7 +39063,7 @@
       <c r="J30" t="n">
         <v>34.98</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -39085,7 +39075,7 @@
       <c r="N30" t="n">
         <v>31.61</v>
       </c>
-      <c r="O30" s="13" t="n">
+      <c r="O30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="P30" t="n">
@@ -39097,7 +39087,7 @@
       <c r="R30" t="n">
         <v>19.37</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="T30" t="n">
@@ -39109,7 +39099,7 @@
       <c r="V30" t="n">
         <v>29.01</v>
       </c>
-      <c r="W30" s="13" t="n">
+      <c r="W30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="X30" t="n">
@@ -39121,7 +39111,7 @@
       <c r="Z30" t="n">
         <v>14.41</v>
       </c>
-      <c r="AA30" s="13" t="n">
+      <c r="AA30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AB30" t="n">
@@ -39133,7 +39123,7 @@
       <c r="AD30" t="n">
         <v>7.85</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -39147,7 +39137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -39156,7 +39146,7 @@
       <c r="C31" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="E31" t="n">
@@ -39165,7 +39155,7 @@
       <c r="F31" t="n">
         <v>25.69</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="H31" t="n">
@@ -39177,7 +39167,7 @@
       <c r="J31" t="n">
         <v>26.43</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -39189,7 +39179,7 @@
       <c r="N31" t="n">
         <v>27.93</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="P31" t="n">
@@ -39201,7 +39191,7 @@
       <c r="R31" t="n">
         <v>28.08</v>
       </c>
-      <c r="S31" s="13" t="n">
+      <c r="S31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="T31" t="n">
@@ -39213,7 +39203,7 @@
       <c r="V31" t="n">
         <v>31.65</v>
       </c>
-      <c r="W31" s="13" t="n">
+      <c r="W31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="X31" t="n">
@@ -39225,7 +39215,7 @@
       <c r="Z31" t="n">
         <v>17.28</v>
       </c>
-      <c r="AA31" s="13" t="n">
+      <c r="AA31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AB31" t="n">
@@ -39237,7 +39227,7 @@
       <c r="AD31" t="n">
         <v>10.83</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -43246,7 +43236,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -43261,7 +43251,7 @@
       <c r="E30" t="n">
         <v>20.85</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="G30" t="n">
@@ -43276,7 +43266,7 @@
       <c r="J30" t="n">
         <v>28.45</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -43291,7 +43281,7 @@
       <c r="O30" t="n">
         <v>34.98</v>
       </c>
-      <c r="P30" s="13" t="n">
+      <c r="P30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="Q30" t="n">
@@ -43306,7 +43296,7 @@
       <c r="T30" t="n">
         <v>34.02</v>
       </c>
-      <c r="U30" s="13" t="n">
+      <c r="U30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="V30" t="n">
@@ -43321,7 +43311,7 @@
       <c r="Y30" t="n">
         <v>21.34</v>
       </c>
-      <c r="Z30" s="13" t="n">
+      <c r="Z30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="AA30" t="n">
@@ -43336,7 +43326,7 @@
       <c r="AD30" t="n">
         <v>29.78</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -43351,7 +43341,7 @@
       <c r="AI30" t="n">
         <v>20.22</v>
       </c>
-      <c r="AJ30" s="13" t="n">
+      <c r="AJ30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AK30" t="n">
@@ -43366,7 +43356,7 @@
       <c r="AN30" t="n">
         <v>8.96</v>
       </c>
-      <c r="AO30" s="13" t="n">
+      <c r="AO30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AP30" t="n">
@@ -43383,7 +43373,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -43398,7 +43388,7 @@
       <c r="E31" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="G31" t="n">
@@ -43413,7 +43403,7 @@
       <c r="J31" t="n">
         <v>25.69</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -43428,7 +43418,7 @@
       <c r="O31" t="n">
         <v>26.63</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="Q31" t="n">
@@ -43443,7 +43433,7 @@
       <c r="T31" t="n">
         <v>27.93</v>
       </c>
-      <c r="U31" s="13" t="n">
+      <c r="U31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="V31" t="n">
@@ -43458,7 +43448,7 @@
       <c r="Y31" t="n">
         <v>30.47</v>
       </c>
-      <c r="Z31" s="13" t="n">
+      <c r="Z31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="AA31" t="n">
@@ -43473,7 +43463,7 @@
       <c r="AD31" t="n">
         <v>31.72</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">
@@ -43488,7 +43478,7 @@
       <c r="AI31" t="n">
         <v>19.37</v>
       </c>
-      <c r="AJ31" s="13" t="n">
+      <c r="AJ31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AK31" t="n">
@@ -43503,7 +43493,7 @@
       <c r="AN31" t="n">
         <v>12.44</v>
       </c>
-      <c r="AO31" s="13" t="n">
+      <c r="AO31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AP31" t="n">
@@ -46556,7 +46546,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="B30" t="n">
@@ -46565,7 +46555,7 @@
       <c r="C30" t="n">
         <v>100</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="E30" t="n">
@@ -46574,7 +46564,7 @@
       <c r="F30" t="n">
         <v>100</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="H30" t="n">
@@ -46586,7 +46576,7 @@
       <c r="J30" t="n">
         <v>100</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="L30" t="n">
@@ -46598,7 +46588,7 @@
       <c r="N30" t="n">
         <v>100</v>
       </c>
-      <c r="O30" s="13" t="n">
+      <c r="O30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="P30" t="n">
@@ -46610,7 +46600,7 @@
       <c r="R30" t="n">
         <v>100</v>
       </c>
-      <c r="S30" s="13" t="n">
+      <c r="S30" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="T30" t="n">
@@ -46622,7 +46612,7 @@
       <c r="V30" t="n">
         <v>100</v>
       </c>
-      <c r="W30" s="13" t="n">
+      <c r="W30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="X30" t="n">
@@ -46634,7 +46624,7 @@
       <c r="Z30" t="n">
         <v>100</v>
       </c>
-      <c r="AA30" s="13" t="n">
+      <c r="AA30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AB30" t="n">
@@ -46646,7 +46636,7 @@
       <c r="AD30" t="n">
         <v>100</v>
       </c>
-      <c r="AE30" s="13" t="n">
+      <c r="AE30" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="AF30" t="n">
@@ -46660,7 +46650,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="B31" t="n">
@@ -46669,7 +46659,7 @@
       <c r="C31" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="E31" t="n">
@@ -46678,7 +46668,7 @@
       <c r="F31" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="H31" t="n">
@@ -46690,7 +46680,7 @@
       <c r="J31" t="n">
         <v>73.68</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="L31" t="n">
@@ -46702,7 +46692,7 @@
       <c r="N31" t="n">
         <v>100</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="P31" t="n">
@@ -46714,7 +46704,7 @@
       <c r="R31" t="n">
         <v>81.82</v>
       </c>
-      <c r="S31" s="13" t="n">
+      <c r="S31" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="T31" t="n">
@@ -46726,7 +46716,7 @@
       <c r="V31" t="n">
         <v>100</v>
       </c>
-      <c r="W31" s="13" t="n">
+      <c r="W31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="X31" t="n">
@@ -46738,7 +46728,7 @@
       <c r="Z31" t="n">
         <v>72.22</v>
       </c>
-      <c r="AA31" s="13" t="n">
+      <c r="AA31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AB31" t="n">
@@ -46750,7 +46740,7 @@
       <c r="AD31" t="n">
         <v>100</v>
       </c>
-      <c r="AE31" s="13" t="n">
+      <c r="AE31" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AF31" t="n">

--- a/Data/CERP_PBC_WQ_Summary_Data.xlsx
+++ b/Data/CERP_PBC_WQ_Summary_Data.xlsx
@@ -5096,6 +5096,318 @@
         <v>5.7</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.22</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.45</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9362,6 +9674,417 @@
         <v>57.14</v>
       </c>
       <c r="AS31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="N32" t="n">
+        <v>80</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>81.29</v>
+      </c>
+      <c r="R32" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="T32" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="W32" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="X32" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>100</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>100</v>
+      </c>
+      <c r="O33" t="n">
+        <v>100</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S33" t="n">
+        <v>94.74</v>
+      </c>
+      <c r="T33" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>100</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>70.71</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>79.1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>95.46</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="I34" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M34" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="N34" t="n">
+        <v>50</v>
+      </c>
+      <c r="O34" t="n">
+        <v>100</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>80</v>
+      </c>
+      <c r="R34" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="S34" t="n">
+        <v>40</v>
+      </c>
+      <c r="T34" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>100</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS34" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12599,6 +13322,318 @@
         <v>31.1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -16850,6 +17885,417 @@
       </c>
       <c r="AS31" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D32" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I32" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X32" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I33" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N33" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X33" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>23</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S34" t="n">
+        <v>24</v>
+      </c>
+      <c r="T34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>24.2</v>
       </c>
     </row>
   </sheetData>
@@ -21121,6 +22567,417 @@
         <v>7.49</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8.22</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9.45</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="O34" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>7.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -24365,6 +26222,318 @@
       </c>
       <c r="AH31" t="n">
         <v>82.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>93.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>79.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>100</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>88.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>90.6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>84.9</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>86.9</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>70.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>73.9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>86.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>85.6</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>82.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>76</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="V34" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>88</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>86.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>95.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>94.4</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>90.2</v>
       </c>
     </row>
   </sheetData>
@@ -28729,6 +30898,417 @@
         <v>107.7</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="D32" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="I32" t="n">
+        <v>93.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>85.07</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="N32" t="n">
+        <v>79.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="R32" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="S32" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="W32" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="X32" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>88.6</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>86.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D33" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I33" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="N33" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="S33" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="W33" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="X33" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>73.9</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>103.17</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>86.43</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>85.6</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>81.57</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>76</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>88.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I34" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="M34" t="n">
+        <v>8.37</v>
+      </c>
+      <c r="N34" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>107.57</v>
+      </c>
+      <c r="R34" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S34" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>83.13</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9.87</v>
+      </c>
+      <c r="X34" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>86.4</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>95.4</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>92.43</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>94.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -31858,6 +34438,318 @@
       </c>
       <c r="AH31" t="n">
         <v>7.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.12</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M33" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>7.79</v>
       </c>
     </row>
   </sheetData>
@@ -35994,6 +38886,417 @@
         <v>8.01</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="O32" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.04</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8.12</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="O34" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>7.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -39238,6 +42541,318 @@
       </c>
       <c r="AH31" t="n">
         <v>12.95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="J32" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="N32" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8.45</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="C33" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="F33" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="I33" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="J33" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="N33" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="U33" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="C34" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="F34" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="I34" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="J34" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="M34" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="N34" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>31</v>
+      </c>
+      <c r="U34" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="V34" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>15.29</v>
       </c>
     </row>
   </sheetData>
@@ -43509,6 +47124,417 @@
         <v>14.03</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="O32" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S32" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="T32" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>8.45</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D33" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="G33" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I33" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="J33" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="O33" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="T33" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D34" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="E34" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I34" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="J34" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="O34" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="T34" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="V34" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>21.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -46753,6 +50779,318 @@
         <v>57.14</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="H32" t="n">
+        <v>80</v>
+      </c>
+      <c r="I32" t="n">
+        <v>85.11</v>
+      </c>
+      <c r="J32" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="M32" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" t="n">
+        <v>100</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="P32" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>100</v>
+      </c>
+      <c r="R32" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="U32" t="n">
+        <v>100</v>
+      </c>
+      <c r="V32" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="X32" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="L33" t="n">
+        <v>94.74</v>
+      </c>
+      <c r="M33" t="n">
+        <v>100</v>
+      </c>
+      <c r="N33" t="n">
+        <v>100</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="P33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="T33" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" t="n">
+        <v>100</v>
+      </c>
+      <c r="V33" t="n">
+        <v>100</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="X33" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" t="n">
+        <v>100</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H34" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" t="n">
+        <v>50</v>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="L34" t="n">
+        <v>40</v>
+      </c>
+      <c r="M34" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" t="n">
+        <v>100</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="P34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>100</v>
+      </c>
+      <c r="R34" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="T34" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" t="n">
+        <v>100</v>
+      </c>
+      <c r="V34" t="n">
+        <v>100</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="X34" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Data/CERP_PBC_WQ_Summary_Data.xlsx
+++ b/Data/CERP_PBC_WQ_Summary_Data.xlsx
@@ -5408,6 +5408,318 @@
         <v>6.96</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>8.39</v>
+      </c>
+      <c r="R36" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8.47</v>
+      </c>
+      <c r="U36" t="n">
+        <v>8.95</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>8.11</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="R37" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10085,6 +10397,417 @@
         <v>100</v>
       </c>
       <c r="AS34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>100</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>100</v>
+      </c>
+      <c r="O35" t="n">
+        <v>100</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>100</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" t="n">
+        <v>100</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>100</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>100</v>
+      </c>
+      <c r="T36" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>100</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>100</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>100</v>
+      </c>
+      <c r="O37" t="n">
+        <v>100</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>100</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>100</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AS37" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13634,6 +14357,318 @@
         <v>24.2</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>22</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U35" t="n">
+        <v>23</v>
+      </c>
+      <c r="V35" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V36" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18296,6 +19331,417 @@
       </c>
       <c r="AS34" t="n">
         <v>24.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S35" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>22</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X35" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>19</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N36" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>19</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I37" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N37" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X37" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>28.4</v>
       </c>
     </row>
   </sheetData>
@@ -22978,6 +24424,417 @@
         <v>7.03</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="O35" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="O36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.39</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.47</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>8.95</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>8.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="O37" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>6.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -26534,6 +28391,318 @@
       </c>
       <c r="AH34" t="n">
         <v>90.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>98.9</v>
+      </c>
+      <c r="M35" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>97</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>89.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>88.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>84.4</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>95.9</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>89.9</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>93.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>93.1</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>98.1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>94.1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>105</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>79.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>74</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>115</v>
+      </c>
+      <c r="U37" t="n">
+        <v>120</v>
+      </c>
+      <c r="V37" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>81.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>95.9</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -31309,6 +33478,417 @@
         <v>94.4</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>103.03</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="N35" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S35" t="n">
+        <v>97</v>
+      </c>
+      <c r="T35" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>90.93</v>
+      </c>
+      <c r="W35" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="X35" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>89.1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>86.6</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>84.4</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>88.6</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>93.77</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>95.9</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>89.9</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D36" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I36" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>103.83</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>103.87</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S36" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>112.57</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X36" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>93.9</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>97.93</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>97.9</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I37" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>94.1</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>108.07</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="N37" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S37" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>78.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="X37" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>115</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>84.07</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>81.1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>92</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -34750,6 +37330,318 @@
       </c>
       <c r="AH34" t="n">
         <v>7.79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="U35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="J36" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>7.66</v>
       </c>
     </row>
   </sheetData>
@@ -39297,6 +42189,417 @@
         <v>7.89</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="O35" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="T35" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X36" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.05</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="J37" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="O37" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S37" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X37" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>7.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -42853,6 +46156,318 @@
       </c>
       <c r="AH34" t="n">
         <v>15.29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="F35" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="I35" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="M35" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="R35" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="U35" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="V35" t="n">
+        <v>33.26</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>18.26</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="C36" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="I36" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="M36" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="N36" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="R36" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="V36" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>21.68</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="C37" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="F37" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="M37" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="N37" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="R37" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="U37" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="V37" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>19.98</v>
       </c>
     </row>
   </sheetData>
@@ -47535,6 +51150,417 @@
         <v>21.85</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I35" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="J35" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N35" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="O35" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="S35" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="T35" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V35" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X35" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>33.26</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>23.21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I36" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="J36" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N36" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="O36" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="S36" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="T36" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V36" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="X36" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>26.01</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="D37" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="E37" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I37" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="N37" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="O37" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S37" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="T37" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="V37" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X37" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>24.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -51091,6 +55117,318 @@
         <v>100</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100</v>
+      </c>
+      <c r="C35" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L35" t="n">
+        <v>100</v>
+      </c>
+      <c r="M35" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" t="n">
+        <v>100</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="P35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>100</v>
+      </c>
+      <c r="R35" t="n">
+        <v>100</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" t="n">
+        <v>100</v>
+      </c>
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100</v>
+      </c>
+      <c r="C36" t="n">
+        <v>100</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="P36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>100</v>
+      </c>
+      <c r="R36" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" t="n">
+        <v>100</v>
+      </c>
+      <c r="V36" t="n">
+        <v>100</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>100</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" t="n">
+        <v>100</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="P37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>100</v>
+      </c>
+      <c r="R37" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="T37" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" t="n">
+        <v>100</v>
+      </c>
+      <c r="V37" t="n">
+        <v>100</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
